--- a/docs/downloads/04/tbl_other_act_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_tous.xlsx
@@ -420,12 +420,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -466,12 +460,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>3.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -489,12 +477,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>3.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -581,12 +563,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -673,12 +649,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>1.6</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -742,12 +712,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -788,12 +752,6 @@
           <t>Ouvrier agricole</t>
         </is>
       </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -811,12 +769,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -834,12 +786,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="E21">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -972,12 +918,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D27">
-        <v>4</v>
-      </c>
-      <c r="E27">
-        <v>4.1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1018,12 +958,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29">
-        <v>4.4</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1064,12 +998,6 @@
           <t>Ouvrier agricole</t>
         </is>
       </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-      <c r="E31">
-        <v>4.4</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1087,12 +1015,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1133,12 +1055,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D34">
-        <v>3</v>
-      </c>
-      <c r="E34">
-        <v>3.5</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1225,12 +1141,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D38">
-        <v>3</v>
-      </c>
-      <c r="E38">
-        <v>3.5</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1248,12 +1158,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1294,12 +1198,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D41">
-        <v>3</v>
-      </c>
-      <c r="E41">
-        <v>5</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1340,12 +1238,6 @@
           <t>Ouvrier agricole</t>
         </is>
       </c>
-      <c r="D43">
-        <v>3</v>
-      </c>
-      <c r="E43">
-        <v>5</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1363,12 +1255,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D44">
-        <v>4</v>
-      </c>
-      <c r="E44">
-        <v>6.7</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1409,12 +1295,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D46">
-        <v>3</v>
-      </c>
-      <c r="E46">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1432,12 +1312,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D47">
-        <v>3</v>
-      </c>
-      <c r="E47">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1478,12 +1352,6 @@
           <t>Ouvrier agricole</t>
         </is>
       </c>
-      <c r="D49">
-        <v>3</v>
-      </c>
-      <c r="E49">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1501,12 +1369,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D50">
-        <v>2</v>
-      </c>
-      <c r="E50">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1570,12 +1432,6 @@
           <t>Ouvrier agricole</t>
         </is>
       </c>
-      <c r="D53">
-        <v>3</v>
-      </c>
-      <c r="E53">
-        <v>5.9</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1593,12 +1449,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D54">
-        <v>3</v>
-      </c>
-      <c r="E54">
-        <v>5.9</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1708,12 +1558,6 @@
           <t>Ouvrier agricole</t>
         </is>
       </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1731,12 +1575,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1754,12 +1592,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D61">
-        <v>2</v>
-      </c>
-      <c r="E61">
-        <v>1.3</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1800,12 +1632,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D63">
-        <v>3</v>
-      </c>
-      <c r="E63">
-        <v>3.4</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1823,12 +1649,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1869,12 +1689,6 @@
           <t>Ouvrier agricole</t>
         </is>
       </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1892,12 +1706,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D67">
-        <v>3</v>
-      </c>
-      <c r="E67">
-        <v>3.4</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1938,12 +1746,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D69">
-        <v>3</v>
-      </c>
-      <c r="E69">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2030,12 +1832,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="D73">
-        <v>3</v>
-      </c>
-      <c r="E73">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2053,12 +1849,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="D74">
-        <v>2</v>
-      </c>
-      <c r="E74">
-        <v>1.5</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2099,12 +1889,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D76">
-        <v>3</v>
-      </c>
-      <c r="E76">
-        <v>2.6</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2122,12 +1906,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77">
-        <v>0.9</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2237,12 +2015,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D82">
-        <v>3</v>
-      </c>
-      <c r="E82">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2375,12 +2147,6 @@
           <t>Chômeur</t>
         </is>
       </c>
-      <c r="D88">
-        <v>4</v>
-      </c>
-      <c r="E88">
-        <v>4.3</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2559,12 +2325,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D96">
-        <v>3</v>
-      </c>
-      <c r="E96">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2674,12 +2434,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D101">
-        <v>2</v>
-      </c>
-      <c r="E101">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2742,12 +2496,6 @@
         <is>
           <t>Éleveur</t>
         </is>
-      </c>
-      <c r="D104">
-        <v>1</v>
-      </c>
-      <c r="E104">
-        <v>0.2</v>
       </c>
     </row>
     <row r="105">

--- a/docs/downloads/04/tbl_other_act_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>31</v>
-      </c>
-      <c r="E2">
-        <v>47.7</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -417,7 +411,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -434,14 +428,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D4">
         <v>29</v>
       </c>
       <c r="E4">
-        <v>44.6</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -457,7 +451,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -474,7 +468,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -491,37 +485,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>72.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D8">
         <v>8</v>
       </c>
       <c r="E8">
-        <v>27.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="9">
@@ -537,14 +531,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D9">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="E9">
-        <v>52.4</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="10">
@@ -560,8 +554,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>20.3</v>
       </c>
     </row>
     <row r="11">
@@ -577,14 +577,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>13</v>
-      </c>
-      <c r="E11">
-        <v>10.3</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -600,14 +594,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D12">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>11.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="13">
@@ -630,7 +624,7 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>16.7</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="14">
@@ -646,8 +640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>7</v>
+      </c>
+      <c r="E14">
+        <v>9.5</v>
       </c>
     </row>
     <row r="15">
@@ -658,19 +658,13 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>6</v>
-      </c>
-      <c r="E15">
-        <v>4.8</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -686,14 +680,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D16">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="E16">
-        <v>78.8</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="17">
@@ -709,8 +703,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17">
+        <v>25.9</v>
       </c>
     </row>
     <row r="18">
@@ -726,14 +726,8 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>7</v>
-      </c>
-      <c r="E18">
-        <v>8.800000000000001</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -766,24 +760,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>18.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -800,14 +800,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D22">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E22">
-        <v>44.9</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="23">
@@ -823,14 +823,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E23">
-        <v>5.1</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="24">
@@ -846,14 +846,8 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>10</v>
-      </c>
-      <c r="E24">
-        <v>10.2</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -869,14 +863,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D25">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>28.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="26">
@@ -892,14 +886,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26">
-        <v>7.1</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="27">
@@ -910,13 +904,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>15</v>
+      </c>
+      <c r="E27">
+        <v>53.6</v>
       </c>
     </row>
     <row r="28">
@@ -932,14 +932,8 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>46</v>
-      </c>
-      <c r="E28">
-        <v>67.59999999999999</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -955,7 +949,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -972,14 +966,8 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>15</v>
-      </c>
-      <c r="E30">
-        <v>22.1</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -995,24 +983,30 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>6</v>
+      </c>
+      <c r="E31">
+        <v>21.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -1029,14 +1023,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D33">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E33">
-        <v>52.3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -1052,8 +1046,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>16</v>
+      </c>
+      <c r="E34">
+        <v>34</v>
       </c>
     </row>
     <row r="35">
@@ -1069,14 +1069,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>8.1</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="36">
@@ -1092,14 +1092,8 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>16</v>
-      </c>
-      <c r="E36">
-        <v>18.6</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1122,7 +1116,7 @@
         <v>11</v>
       </c>
       <c r="E37">
-        <v>12.8</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="38">
@@ -1138,8 +1132,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38">
+        <v>10.6</v>
       </c>
     </row>
     <row r="39">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -1172,14 +1172,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D40">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E40">
-        <v>65</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="41">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -1212,14 +1212,8 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>11</v>
-      </c>
-      <c r="E42">
-        <v>18.3</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1252,7 +1246,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -1269,14 +1263,8 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>43</v>
-      </c>
-      <c r="E45">
-        <v>51.2</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1292,8 +1280,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>30</v>
+      </c>
+      <c r="E46">
+        <v>68.2</v>
       </c>
     </row>
     <row r="47">
@@ -1309,7 +1303,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -1326,14 +1320,8 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>30</v>
-      </c>
-      <c r="E48">
-        <v>35.7</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1349,8 +1337,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>11.4</v>
       </c>
     </row>
     <row r="50">
@@ -1361,12 +1355,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -1383,14 +1377,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D51">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="E51">
-        <v>74.5</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="52">
@@ -1406,14 +1400,8 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>7</v>
-      </c>
-      <c r="E52">
-        <v>13.7</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1446,8 +1434,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>6</v>
+      </c>
+      <c r="E54">
+        <v>27.3</v>
       </c>
     </row>
     <row r="55">
@@ -1463,14 +1457,8 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D55">
-        <v>70</v>
-      </c>
-      <c r="E55">
-        <v>44.9</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1486,14 +1474,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D56">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E56">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="57">
@@ -1509,14 +1497,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D57">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="E57">
-        <v>7.1</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="58">
@@ -1532,14 +1520,8 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D58">
-        <v>64</v>
-      </c>
-      <c r="E58">
-        <v>41</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1555,7 +1537,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1554,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
@@ -1589,8 +1571,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D61">
+        <v>11</v>
+      </c>
+      <c r="E61">
+        <v>11.5</v>
       </c>
     </row>
     <row r="62">
@@ -1606,14 +1594,8 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D62">
-        <v>67</v>
-      </c>
-      <c r="E62">
-        <v>75.3</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -1629,8 +1611,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D63">
+        <v>14</v>
+      </c>
+      <c r="E63">
+        <v>58.3</v>
       </c>
     </row>
     <row r="64">
@@ -1646,7 +1634,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -1663,14 +1651,8 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D65">
-        <v>14</v>
-      </c>
-      <c r="E65">
-        <v>15.7</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -1703,7 +1685,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -1720,14 +1702,8 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D68">
-        <v>53</v>
-      </c>
-      <c r="E68">
-        <v>39</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1743,8 +1719,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chômeur</t>
-        </is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>13</v>
+      </c>
+      <c r="E69">
+        <v>14.4</v>
       </c>
     </row>
     <row r="70">
@@ -1760,14 +1742,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D70">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="E70">
-        <v>8.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="71">
@@ -1783,14 +1765,8 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D71">
-        <v>55</v>
-      </c>
-      <c r="E71">
-        <v>40.4</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -1806,14 +1782,8 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D72">
-        <v>9</v>
-      </c>
-      <c r="E72">
-        <v>6.6</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -1829,8 +1799,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>9</v>
+      </c>
+      <c r="E73">
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -1846,8 +1822,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>6</v>
+      </c>
+      <c r="E74">
+        <v>6.7</v>
       </c>
     </row>
     <row r="75">
@@ -1863,14 +1845,8 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D75">
-        <v>76</v>
-      </c>
-      <c r="E75">
-        <v>66.7</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -1886,7 +1862,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -1903,8 +1879,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>22</v>
+      </c>
+      <c r="E77">
+        <v>48.9</v>
       </c>
     </row>
     <row r="78">
@@ -1920,14 +1902,8 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D78">
-        <v>22</v>
-      </c>
-      <c r="E78">
-        <v>19.3</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -1943,14 +1919,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D79">
         <v>6</v>
       </c>
       <c r="E79">
-        <v>5.3</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="80">
@@ -1966,37 +1942,37 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D80">
         <v>6</v>
       </c>
       <c r="E80">
-        <v>5.3</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D81">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E81">
-        <v>42.1</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="82">
@@ -2012,7 +1988,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -2029,14 +2005,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D83">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E83">
-        <v>4.8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="84">
@@ -2052,14 +2028,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D84">
         <v>52</v>
       </c>
       <c r="E84">
-        <v>41.3</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="85">
@@ -2075,14 +2051,8 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D85">
-        <v>5</v>
-      </c>
-      <c r="E85">
-        <v>4</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -2098,14 +2068,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D86">
         <v>7</v>
       </c>
       <c r="E86">
-        <v>5.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="87">
@@ -2116,19 +2086,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D87">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E87">
-        <v>72.3</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="88">
@@ -2139,12 +2109,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -2161,14 +2131,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D89">
         <v>17</v>
       </c>
       <c r="E89">
-        <v>18.1</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="90">
@@ -2184,60 +2154,54 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D90">
-        <v>5</v>
-      </c>
-      <c r="E90">
-        <v>5.3</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D91">
-        <v>405</v>
+        <v>5</v>
       </c>
       <c r="E91">
-        <v>46.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D92">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E92">
-        <v>3.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93">
@@ -2253,14 +2217,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D93">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="E93">
-        <v>7.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="94">
@@ -2276,14 +2240,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D94">
-        <v>289</v>
+        <v>71</v>
       </c>
       <c r="E94">
-        <v>33</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="95">
@@ -2299,14 +2263,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D95">
-        <v>57</v>
+        <v>289</v>
       </c>
       <c r="E95">
-        <v>6.5</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="96">
@@ -2322,8 +2286,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D96">
+        <v>19</v>
+      </c>
+      <c r="E96">
+        <v>3.6</v>
       </c>
     </row>
     <row r="97">
@@ -2339,14 +2309,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D97">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E97">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="98">
@@ -2362,14 +2332,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D98">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="99">
@@ -2380,19 +2350,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D99">
-        <v>418</v>
+        <v>46</v>
       </c>
       <c r="E99">
-        <v>71.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -2408,14 +2378,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D100">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E100">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="101">
@@ -2431,7 +2401,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -2448,14 +2418,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D102">
         <v>101</v>
       </c>
       <c r="E102">
-        <v>17.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="103">
@@ -2471,14 +2441,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D103">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E103">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="104">
@@ -2494,8 +2464,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="D104">
+        <v>25</v>
+      </c>
+      <c r="E104">
+        <v>11.8</v>
       </c>
     </row>
     <row r="105">
@@ -2511,14 +2487,37 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D105">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E105">
-        <v>4.3</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D106">
+        <v>38</v>
+      </c>
+      <c r="E106">
+        <v>17.9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_other_act_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -401,7 +401,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -418,7 +418,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -458,7 +458,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -498,7 +498,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -544,7 +544,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -630,7 +630,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -716,7 +716,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -790,7 +790,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -876,7 +876,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -922,7 +922,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -973,7 +973,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -996,7 +996,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1082,7 +1082,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1122,7 +1122,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1185,7 +1185,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1219,7 +1219,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1253,7 +1253,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1327,7 +1327,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1350,7 +1350,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1390,7 +1390,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1407,7 +1407,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1464,7 +1464,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1510,7 +1510,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1527,7 +1527,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1544,7 +1544,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1584,7 +1584,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1692,7 +1692,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1709,7 +1709,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1732,7 +1732,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1812,7 +1812,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1869,7 +1869,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1892,7 +1892,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1909,7 +1909,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1932,7 +1932,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1955,7 +1955,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1978,7 +1978,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1995,7 +1995,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2018,7 +2018,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2041,7 +2041,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2058,7 +2058,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2081,7 +2081,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2104,7 +2104,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2121,7 +2121,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2144,7 +2144,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2184,7 +2184,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2207,7 +2207,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2230,7 +2230,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2276,7 +2276,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2345,7 +2345,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2368,7 +2368,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2391,7 +2391,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2408,7 +2408,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2454,7 +2454,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2477,7 +2477,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2500,7 +2500,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">

--- a/docs/downloads/04/tbl_other_act_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -617,14 +617,8 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>21</v>
-      </c>
-      <c r="E13">
-        <v>28.4</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -640,14 +634,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E14">
-        <v>9.5</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="15">
@@ -658,12 +652,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -680,14 +674,8 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>7</v>
-      </c>
-      <c r="E16">
-        <v>25.9</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -703,7 +691,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D17">
@@ -726,8 +714,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>7</v>
+      </c>
+      <c r="E18">
+        <v>25.9</v>
       </c>
     </row>
     <row r="19">
@@ -743,7 +737,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -760,54 +754,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>5</v>
-      </c>
-      <c r="E20">
-        <v>18.5</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ambodivoara</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ambodivoara</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>12</v>
-      </c>
-      <c r="E22">
-        <v>19.7</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -823,14 +805,8 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>28</v>
-      </c>
-      <c r="E23">
-        <v>45.9</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -846,8 +822,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>12</v>
+      </c>
+      <c r="E24">
+        <v>19.7</v>
       </c>
     </row>
     <row r="25">
@@ -863,14 +845,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E25">
-        <v>11.5</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="26">
@@ -886,14 +868,8 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>8</v>
-      </c>
-      <c r="E26">
-        <v>13.1</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -904,19 +880,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="D27">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>53.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -927,13 +903,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>7</v>
+      </c>
+      <c r="E28">
+        <v>11.5</v>
       </c>
     </row>
     <row r="29">
@@ -944,12 +926,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -966,8 +948,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>15</v>
+      </c>
+      <c r="E30">
+        <v>53.6</v>
       </c>
     </row>
     <row r="31">
@@ -983,100 +971,76 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>6</v>
-      </c>
-      <c r="E31">
-        <v>21.4</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ambohidrony</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ambohidrony</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>8</v>
-      </c>
-      <c r="E33">
-        <v>17</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ambohidrony</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>16</v>
-      </c>
-      <c r="E34">
-        <v>34</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ambohidrony</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>5</v>
-      </c>
-      <c r="E35">
-        <v>10.6</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1092,7 +1056,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -1109,14 +1073,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D37">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E37">
-        <v>23.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -1132,14 +1096,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E38">
-        <v>10.6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
@@ -1150,13 +1114,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <v>10.6</v>
       </c>
     </row>
     <row r="40">
@@ -1167,19 +1137,13 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>11</v>
-      </c>
-      <c r="E40">
-        <v>39.3</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1190,12 +1154,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
     </row>
@@ -1207,13 +1171,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>11</v>
+      </c>
+      <c r="E42">
+        <v>23.4</v>
       </c>
     </row>
     <row r="43">
@@ -1224,12 +1194,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -1246,59 +1216,59 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>11</v>
+      </c>
+      <c r="E45">
+        <v>39.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>30</v>
-      </c>
-      <c r="E46">
-        <v>68.2</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1310,47 +1280,41 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>5</v>
-      </c>
-      <c r="E49">
-        <v>11.4</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1360,7 +1324,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -1372,19 +1336,13 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>7</v>
-      </c>
-      <c r="E51">
-        <v>31.8</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1395,13 +1353,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>30</v>
+      </c>
+      <c r="E52">
+        <v>68.2</v>
       </c>
     </row>
     <row r="53">
@@ -1412,12 +1376,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -1429,25 +1393,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>6</v>
-      </c>
-      <c r="E54">
-        <v>27.3</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1457,14 +1415,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1474,65 +1432,59 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="D56">
-        <v>12</v>
-      </c>
-      <c r="E56">
-        <v>12.5</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D57">
-        <v>64</v>
-      </c>
-      <c r="E57">
-        <v>66.7</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>7</v>
+      </c>
+      <c r="E58">
+        <v>31.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1544,12 +1496,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1561,12 +1513,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1575,10 +1527,10 @@
         </is>
       </c>
       <c r="D61">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E61">
-        <v>11.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="62">
@@ -1589,12 +1541,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -1606,19 +1558,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D63">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E63">
-        <v>58.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="64">
@@ -1629,13 +1581,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D64">
+        <v>64</v>
+      </c>
+      <c r="E64">
+        <v>66.7</v>
       </c>
     </row>
     <row r="65">
@@ -1646,12 +1604,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1621,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -1680,19 +1638,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>7</v>
+      </c>
+      <c r="E67">
+        <v>7.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1702,14 +1666,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1719,123 +1683,105 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="D69">
-        <v>13</v>
-      </c>
-      <c r="E69">
-        <v>14.4</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D70">
-        <v>55</v>
-      </c>
-      <c r="E70">
-        <v>61.1</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>14</v>
+      </c>
+      <c r="E71">
+        <v>58.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D73">
-        <v>9</v>
-      </c>
-      <c r="E73">
-        <v>10</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
-      </c>
-      <c r="D74">
-        <v>6</v>
-      </c>
-      <c r="E74">
-        <v>6.7</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1845,14 +1791,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1862,7 +1808,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -1874,19 +1820,13 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D77">
-        <v>22</v>
-      </c>
-      <c r="E77">
-        <v>48.9</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -1897,13 +1837,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D78">
+        <v>13</v>
+      </c>
+      <c r="E78">
+        <v>14.4</v>
       </c>
     </row>
     <row r="79">
@@ -1914,19 +1860,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D79">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="E79">
-        <v>13.3</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="80">
@@ -1937,19 +1883,13 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D80">
-        <v>6</v>
-      </c>
-      <c r="E80">
-        <v>13.3</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -1960,25 +1900,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
-      </c>
-      <c r="D81">
-        <v>7</v>
-      </c>
-      <c r="E81">
-        <v>15.6</v>
+          <t>Elève / Etudiant</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1988,14 +1922,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2005,20 +1939,20 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D83">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E83">
-        <v>8.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2028,100 +1962,88 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D84">
-        <v>52</v>
-      </c>
-      <c r="E84">
-        <v>65.8</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
-      </c>
-      <c r="D86">
-        <v>7</v>
-      </c>
-      <c r="E86">
-        <v>8.9</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E87">
-        <v>6.3</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2131,20 +2053,20 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D89">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E89">
-        <v>56.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2154,14 +2076,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2171,20 +2093,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E91">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2196,18 +2118,12 @@
         <is>
           <t>Services &amp; Autres</t>
         </is>
-      </c>
-      <c r="D92">
-        <v>6</v>
-      </c>
-      <c r="E92">
-        <v>20</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2219,18 +2135,12 @@
         <is>
           <t>Artisanat, BTP &amp; Transport</t>
         </is>
-      </c>
-      <c r="D93">
-        <v>18</v>
-      </c>
-      <c r="E93">
-        <v>3.4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2244,16 +2154,16 @@
         </is>
       </c>
       <c r="D94">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="E94">
-        <v>13.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2267,16 +2177,16 @@
         </is>
       </c>
       <c r="D95">
-        <v>289</v>
+        <v>52</v>
       </c>
       <c r="E95">
-        <v>54.9</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2288,18 +2198,12 @@
         <is>
           <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
-      </c>
-      <c r="D96">
-        <v>19</v>
-      </c>
-      <c r="E96">
-        <v>3.6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2313,16 +2217,16 @@
         </is>
       </c>
       <c r="D97">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E97">
-        <v>4.9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2332,20 +2236,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D98">
-        <v>57</v>
-      </c>
-      <c r="E98">
-        <v>10.8</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2355,43 +2253,37 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D99">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="E99">
-        <v>8.699999999999999</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
-      </c>
-      <c r="D100">
-        <v>11</v>
-      </c>
-      <c r="E100">
-        <v>5.2</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2401,14 +2293,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D101">
+        <v>17</v>
+      </c>
+      <c r="E101">
+        <v>56.7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2418,20 +2316,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D102">
-        <v>101</v>
-      </c>
-      <c r="E102">
-        <v>47.6</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2441,20 +2333,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D103">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E103">
-        <v>7.5</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2464,20 +2356,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Elève / Etudiant</t>
-        </is>
-      </c>
-      <c r="D104">
-        <v>25</v>
-      </c>
-      <c r="E104">
-        <v>11.8</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2487,14 +2373,8 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D105">
-        <v>19</v>
-      </c>
-      <c r="E105">
-        <v>9</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -2505,19 +2385,358 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D106">
+        <v>18</v>
+      </c>
+      <c r="E106">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D107">
+        <v>71</v>
+      </c>
+      <c r="E107">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D108">
+        <v>289</v>
+      </c>
+      <c r="E108">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D109">
+        <v>19</v>
+      </c>
+      <c r="E109">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="D110">
+        <v>26</v>
+      </c>
+      <c r="E110">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="D111">
+        <v>27</v>
+      </c>
+      <c r="E111">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D112">
+        <v>57</v>
+      </c>
+      <c r="E112">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
           <t>Services &amp; Autres</t>
         </is>
       </c>
-      <c r="D106">
-        <v>38</v>
-      </c>
-      <c r="E106">
-        <v>17.9</v>
+      <c r="D113">
+        <v>19</v>
+      </c>
+      <c r="E113">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D114">
+        <v>11</v>
+      </c>
+      <c r="E114">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D116">
+        <v>101</v>
+      </c>
+      <c r="E116">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D117">
+        <v>16</v>
+      </c>
+      <c r="E117">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="D118">
+        <v>25</v>
+      </c>
+      <c r="E118">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="D119">
+        <v>19</v>
+      </c>
+      <c r="E119">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D120">
+        <v>19</v>
+      </c>
+      <c r="E120">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D121">
+        <v>19</v>
+      </c>
+      <c r="E121">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
